--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -965,9 +965,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2714,51 +2714,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2792,16 +2788,16 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2809,7 +2805,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2852,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,51 +2860,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3006,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3014,10 +3006,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3026,39 +3016,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3092,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3126,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3203,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3236,22 +3224,22 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
@@ -3276,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3353,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3383,20 +3371,20 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3405,11 +3393,11 @@
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3426,12 +3414,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3503,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3533,16 +3521,16 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3551,15 +3539,15 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3576,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3653,12 +3641,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3683,20 +3671,20 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3705,11 +3693,11 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3726,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3756,7 +3744,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3764,8 +3752,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3774,37 +3764,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3829,33 +3821,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3872,12 +3864,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3902,7 +3894,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3910,47 +3902,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3975,7 +3971,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3984,24 +3980,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>34</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4018,12 +4014,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4048,7 +4044,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4056,47 +4052,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4124,17 +4124,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4203,11 +4203,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4267,33 +4267,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4349,11 +4349,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4422,24 +4422,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4495,11 +4495,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4568,11 +4568,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>11</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4635,17 +4635,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4714,11 +4714,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4796,15 +4796,15 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4854,17 +4854,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4932,51 +4932,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5001,33 +4997,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5044,12 +5040,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5074,59 +5070,55 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5151,33 +5143,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5194,12 +5186,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5224,7 +5216,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5233,7 +5225,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5242,15 +5234,15 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>500,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5267,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5297,33 +5289,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5340,12 +5332,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5370,7 +5362,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5378,47 +5370,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5443,33 +5439,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5486,12 +5482,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5516,7 +5512,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5524,47 +5520,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5589,33 +5589,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5705,12 +5705,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5744,24 +5744,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5819,9 +5819,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5851,12 +5851,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5890,11 +5890,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5957,17 +5957,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6030,17 +6030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6118,30 +6118,468 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1470,20 +1470,20 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1549,9 +1549,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1766,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1987,9 +1987,9 @@
       <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2425,9 +2425,9 @@
       <c r="I27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3152,10 +3152,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3164,41 +3162,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3221,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3341,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3371,7 +3367,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3382,22 +3378,22 @@
       <c r="I40" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3414,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3491,14 +3487,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3524,17 +3520,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,12 +3560,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3641,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3671,16 +3667,16 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3693,11 +3689,11 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3714,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3791,14 +3787,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3821,20 +3817,20 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>▲ 404,8%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3843,11 +3839,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3864,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3941,14 +3937,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3971,33 +3967,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4014,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4091,14 +4087,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4121,33 +4117,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4164,14 +4160,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4194,7 +4190,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4202,8 +4198,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4212,39 +4210,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4267,33 +4267,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4310,14 +4310,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4351,9 +4351,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4383,14 +4383,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4413,33 +4413,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4456,14 +4456,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4495,11 +4495,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4529,14 +4529,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4568,24 +4568,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4602,14 +4602,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4641,11 +4641,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4675,14 +4675,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4714,11 +4714,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4748,14 +4748,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4787,11 +4787,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4821,14 +4821,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4894,14 +4894,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4933,11 +4933,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4967,14 +4967,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5006,11 +5006,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>6</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5040,14 +5040,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5073,19 +5073,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5113,14 +5113,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5152,11 +5152,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5186,14 +5186,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5216,12 +5216,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -5229,25 +5229,25 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5259,14 +5259,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5292,17 +5292,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5370,10 +5370,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5382,41 +5380,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5439,33 +5435,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5482,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5559,14 +5555,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5589,33 +5585,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5632,14 +5628,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5662,7 +5658,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5670,8 +5666,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5680,39 +5678,41 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5735,33 +5735,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,5%</t>
+        <v>12</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5778,14 +5778,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5819,9 +5819,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5851,14 +5851,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5890,24 +5890,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5924,14 +5924,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5963,11 +5963,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5997,14 +5997,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6030,17 +6030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6070,14 +6070,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6109,11 +6109,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6143,14 +6143,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6173,33 +6173,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6216,14 +6216,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6289,14 +6289,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6328,24 +6328,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6362,14 +6362,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6395,17 +6395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6435,14 +6435,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6474,11 +6474,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6508,78 +6508,224 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L83" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,20 +662,20 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,24 +817,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
           <t>R$ 22,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 45,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1111,9 +1111,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1332,20 +1332,20 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1549,9 +1549,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2571,9 +2571,9 @@
       <c r="I29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,9 +2636,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 22,2%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3298,51 +3298,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3376,16 +3372,16 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3393,7 +3389,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3440,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3448,51 +3444,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3526,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3560,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3590,7 +3582,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3598,10 +3590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3610,39 +3600,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3670,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3710,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3787,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3820,22 +3808,22 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3860,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3937,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3967,20 +3955,20 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3989,11 +3977,11 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4010,12 +3998,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4087,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4117,16 +4105,16 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4135,15 +4123,15 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4160,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4237,12 +4225,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4267,20 +4255,20 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4289,11 +4277,11 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4310,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4340,7 +4328,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4348,8 +4336,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4358,37 +4348,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4413,33 +4405,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4456,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4486,7 +4478,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4494,47 +4486,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4559,7 +4555,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4568,24 +4564,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>34</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4602,12 +4598,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4632,7 +4628,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4640,47 +4636,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4708,17 +4708,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4787,11 +4787,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4851,33 +4851,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4933,11 +4933,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5006,24 +5006,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5079,11 +5079,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5152,11 +5152,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5298,11 +5298,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5380,15 +5380,15 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5438,17 +5438,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5516,51 +5516,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5585,33 +5581,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5628,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5658,59 +5654,55 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5735,33 +5727,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5778,12 +5770,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5808,7 +5800,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5817,7 +5809,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5826,15 +5818,15 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>500,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5851,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5881,33 +5873,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,5%</t>
+        <v>2</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5924,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5954,7 +5946,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5962,47 +5954,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6027,33 +6023,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6070,12 +6066,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6100,7 +6096,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6108,47 +6104,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6173,33 +6173,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6289,12 +6289,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6328,24 +6328,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6403,9 +6403,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6474,11 +6474,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▲ 266,7%</t>
+        <v>23</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6541,17 +6541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6581,12 +6581,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6702,30 +6702,468 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,15 +826,15 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,22 +884,22 @@
           <t>R$ 22,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,1%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -957,9 +957,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,20 +1100,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1122,11 +1122,11 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1255,24 +1255,24 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,13 +1322,13 @@
           <t>R$ 22,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 45,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1483,15 +1483,15 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1549,9 +1549,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1987,9 +1987,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,11 +2423,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3299,11 +3299,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3664,11 +3664,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3736,51 +3736,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3814,16 +3810,16 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3831,7 +3827,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3848,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3878,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3886,51 +3882,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3964,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3998,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4028,7 +4020,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4036,10 +4028,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4048,39 +4038,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4114,11 +4102,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4148,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4225,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4258,22 +4246,22 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
@@ -4298,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4375,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4405,20 +4393,20 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4427,11 +4415,11 @@
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4448,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4525,12 +4513,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4555,16 +4543,16 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4573,15 +4561,15 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4598,12 +4586,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4675,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4705,20 +4693,20 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4727,11 +4715,11 @@
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4748,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4778,7 +4766,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4786,8 +4774,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4796,37 +4786,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4851,33 +4843,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4894,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4924,7 +4916,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4932,47 +4924,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4997,7 +4993,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5006,24 +5002,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>34</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5040,12 +5036,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5070,7 +5066,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5078,47 +5074,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5146,17 +5146,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5186,12 +5186,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5225,11 +5225,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5289,33 +5289,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5371,11 +5371,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5444,24 +5444,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5551,12 +5551,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5590,11 +5590,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>11</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5657,17 +5657,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5736,11 +5736,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5818,15 +5818,15 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5876,17 +5876,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5954,51 +5954,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6023,33 +6019,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6066,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6096,59 +6092,55 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6173,33 +6165,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6216,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6246,7 +6238,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6255,7 +6247,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6264,15 +6256,15 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>500,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6289,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6319,33 +6311,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6362,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6392,7 +6384,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6400,47 +6392,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6465,33 +6461,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6508,12 +6504,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6538,7 +6534,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6546,47 +6542,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6611,33 +6611,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6727,12 +6727,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6766,24 +6766,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6841,9 +6841,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6912,11 +6912,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7019,12 +7019,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7052,17 +7052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7140,30 +7140,468 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -735,20 +735,20 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -757,11 +757,11 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -886,20 +886,20 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -957,13 +957,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1100,20 +1100,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1122,11 +1122,11 @@
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1251,20 +1251,20 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 51,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1410,15 +1410,15 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1695,9 +1695,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2058,11 +2058,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2492,20 +2492,20 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2571,9 +2571,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2715,11 +2715,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3009,9 +3009,9 @@
       <c r="I35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3299,11 +3299,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3447,9 +3447,9 @@
       <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3518,11 +3518,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3658,17 +3658,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3956,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4096,17 +4096,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4174,10 +4174,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4186,41 +4184,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4243,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4286,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4363,14 +4359,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4393,7 +4389,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4404,22 +4400,22 @@
       <c r="I54" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,12 +4432,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4513,14 +4509,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4546,17 +4542,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,12 +4582,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4663,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4693,16 +4689,16 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4715,11 +4711,11 @@
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4736,12 +4732,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4813,14 +4809,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4843,20 +4839,20 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4865,11 +4861,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4886,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4963,14 +4959,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4993,33 +4989,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5036,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5113,14 +5109,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5143,33 +5139,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5186,14 +5182,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5216,7 +5212,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5224,8 +5220,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5234,39 +5232,41 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5289,33 +5289,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5373,9 +5373,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5405,14 +5405,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5435,33 +5435,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5478,14 +5478,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5517,11 +5517,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5551,14 +5551,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5590,24 +5590,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5624,14 +5624,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5663,11 +5663,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5697,14 +5697,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5736,11 +5736,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5770,14 +5770,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5809,11 +5809,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5843,14 +5843,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5882,11 +5882,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5916,14 +5916,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5955,11 +5955,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5989,14 +5989,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6028,11 +6028,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6062,14 +6062,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6095,19 +6095,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6135,14 +6135,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6174,11 +6174,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6208,14 +6208,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
@@ -6251,25 +6251,25 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6281,14 +6281,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6314,17 +6314,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6354,14 +6354,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6392,10 +6392,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6404,41 +6402,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6461,33 +6457,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6504,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6581,14 +6577,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6611,33 +6607,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6654,14 +6650,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6684,7 +6680,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6692,8 +6688,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6702,39 +6700,41 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6757,33 +6757,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6800,14 +6800,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6841,9 +6841,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6873,14 +6873,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6912,24 +6912,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>13</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6946,14 +6946,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6985,11 +6985,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7019,14 +7019,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7052,17 +7052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>23</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7092,14 +7092,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7131,11 +7131,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7165,14 +7165,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7195,33 +7195,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7238,14 +7238,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7311,14 +7311,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7350,24 +7350,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 266,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7384,14 +7384,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7417,17 +7417,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7457,14 +7457,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7496,11 +7496,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7530,78 +7530,224 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="n">
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L97" s="2" t="n">
+      <c r="L99" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,20 +881,20 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,20 +1173,20 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,20 +1246,20 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1268,11 +1268,11 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1332,20 +1332,20 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,16 +1392,16 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1410,15 +1410,15 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,20 +1538,20 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1702,15 +1702,15 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -1770,20 +1770,20 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1841,9 +1841,9 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 45,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2206,22 +2206,22 @@
       <c r="I24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2344,17 +2344,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2425,9 +2425,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2717,9 +2717,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2861,11 +2861,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2934,24 +2934,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3155,9 +3155,9 @@
       <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3299,11 +3299,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3372,24 +3372,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3447,9 +3447,9 @@
       <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3512,17 +3512,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3664,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3804,17 +3804,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>4</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3956,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4096,17 +4096,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4175,11 +4175,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4320,51 +4320,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4389,7 +4385,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4398,24 +4394,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4432,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4462,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4470,10 +4466,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4482,39 +4476,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4542,17 +4534,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,8%</t>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4659,12 +4651,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4689,33 +4681,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4732,12 +4724,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4809,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4839,20 +4831,20 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4861,11 +4853,11 @@
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4959,12 +4951,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4989,20 +4981,20 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>▲ 404,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5011,11 +5003,11 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5032,12 +5024,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5109,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5142,13 +5134,13 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5157,7 +5149,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5182,12 +5174,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5259,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5289,33 +5281,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
+          <t>▲ 404,8%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5332,12 +5324,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5362,7 +5354,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5370,8 +5362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5380,37 +5374,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5438,22 +5434,22 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5461,7 +5457,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5478,12 +5474,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5508,7 +5504,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5516,47 +5512,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5581,33 +5581,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5663,11 +5663,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5727,33 +5727,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5809,11 +5809,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5843,12 +5843,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5882,24 +5882,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5955,11 +5955,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5989,12 +5989,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6028,11 +6028,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6101,11 +6101,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6174,11 +6174,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6241,17 +6241,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6320,11 +6320,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6354,12 +6354,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6393,24 +6393,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6460,17 +6460,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6500,12 +6500,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6530,59 +6530,55 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6607,33 +6603,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6650,12 +6646,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6680,7 +6676,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6688,10 +6684,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6700,39 +6694,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6757,33 +6749,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6800,12 +6792,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6830,7 +6822,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6838,8 +6830,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6848,37 +6842,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6906,22 +6902,22 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,5%</t>
+        <v>5</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -6946,12 +6942,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6976,7 +6972,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6984,47 +6980,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7049,33 +7049,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7131,11 +7131,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7195,33 +7195,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>13</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7277,11 +7277,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7350,24 +7350,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7384,12 +7384,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7423,11 +7423,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7490,17 +7490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7563,17 +7563,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7642,24 +7642,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7676,78 +7676,370 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L99" s="2" t="n">
+      <c r="L103" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,20 +1173,20 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1195,11 +1195,11 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,8 +1254,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>2</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1264,37 +1266,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1330,9 +1334,9 @@
       <c r="I12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1345,7 +1349,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1395,9 +1399,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -1435,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1478,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,12 +1542,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1560,11 +1564,11 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1624,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1697,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,25 +1761,25 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 51,1%</t>
+          <t>R$ 20,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1787,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1843,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,7 +1907,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1912,24 +1916,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1950,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2023,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,9 +2056,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -2062,7 +2066,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2096,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2169,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2199,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2242,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2281,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,12 +2315,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,7 +2345,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2354,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,11 +2427,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2498,9 +2502,9 @@
       <c r="I28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,17 +2640,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,7 +2719,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2749,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2863,9 +2867,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2930,20 +2934,20 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
@@ -2968,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3007,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3041,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,7 +3075,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3080,24 +3084,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3147,17 +3151,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3226,11 +3230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3260,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3294,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3366,17 +3370,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3406,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,7 +3440,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3447,22 +3451,22 @@
       <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,12 +3513,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3527,15 +3531,15 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3629,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 45,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3668,20 +3672,20 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3737,11 +3741,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3804,17 +3808,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3883,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,7 +3951,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,24 +3960,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4029,7 +4033,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4063,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4096,17 +4100,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>4</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4209,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4248,24 +4252,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4321,11 +4325,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,12 +4359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4388,17 +4392,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4432,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4467,7 +4471,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4501,12 +4505,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4535,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4578,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,7 +4608,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4612,10 +4616,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4624,39 +4626,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4724,12 +4724,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4762,51 +4762,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4840,11 +4836,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 43,8%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,12 +4870,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4904,7 +4900,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4912,51 +4908,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4984,17 +4976,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,12 +5016,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5054,7 +5046,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5062,51 +5054,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,20 +5119,20 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5153,11 +5141,11 @@
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5204,7 +5192,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5212,51 +5200,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5281,20 +5265,20 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5303,11 +5287,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5324,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5354,7 +5338,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5362,51 +5346,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5440,16 +5420,16 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5474,12 +5454,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5504,7 +5484,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5512,51 +5492,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5584,17 +5560,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5624,12 +5600,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5663,11 +5639,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5697,12 +5673,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5727,33 +5703,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5770,12 +5746,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5809,11 +5785,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5843,12 +5819,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5873,33 +5849,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5916,12 +5892,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5955,11 +5931,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5989,12 +5965,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6019,7 +5995,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6028,24 +6004,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6062,12 +6038,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6103,9 +6079,9 @@
       <c r="I77" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6135,12 +6111,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6174,11 +6150,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6208,12 +6184,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6247,7 +6223,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6281,12 +6257,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6314,17 +6290,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6354,12 +6330,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6384,7 +6360,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6392,47 +6368,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6457,7 +6437,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6466,24 +6446,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>9</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6500,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6530,55 +6510,59 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6614,9 +6598,9 @@
       <c r="I84" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6646,12 +6630,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6676,7 +6660,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6684,8 +6668,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>1</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6694,37 +6680,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6758,11 +6746,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6792,12 +6780,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6869,12 +6857,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6904,20 +6892,20 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -6925,7 +6913,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6942,12 +6930,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7019,12 +7007,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7049,33 +7037,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7092,12 +7080,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7122,7 +7110,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7130,8 +7118,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7140,37 +7130,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7204,16 +7196,16 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
@@ -7221,7 +7213,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7238,12 +7230,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7268,7 +7260,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7276,47 +7268,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7344,17 +7340,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7384,12 +7380,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7423,11 +7419,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7457,12 +7453,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7487,33 +7483,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7530,12 +7526,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7569,11 +7565,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7603,12 +7599,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7642,16 +7638,16 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7659,7 +7655,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7676,12 +7672,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7715,11 +7711,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7749,12 +7745,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7788,11 +7784,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7822,12 +7818,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7855,17 +7851,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7895,12 +7891,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7934,11 +7930,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7968,78 +7964,1838 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 121,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1323,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1332,16 +1328,16 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1478,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1512,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1618,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1697,7 +1693,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1731,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1761,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1837,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1907,7 +1903,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1916,24 +1912,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1950,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1980,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,7 +1985,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1998,15 +1994,15 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2023,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2056,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2135,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2199,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2242,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2272,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2280,47 +2276,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2345,33 +2345,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2427,11 +2427,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2491,20 +2491,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2573,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2646,24 +2646,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2753,12 +2753,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2786,17 +2786,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2899,12 +2899,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2929,20 +2929,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2951,11 +2951,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3011,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3075,33 +3075,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3151,13 +3151,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3191,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3221,33 +3221,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -3316,11 +3316,11 @@
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3337,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3367,33 +3367,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3458,15 +3458,15 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3513,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 51,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3597,9 +3597,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3668,24 +3668,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3808,17 +3808,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3951,33 +3951,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 45,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4110,20 +4110,20 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4179,11 +4179,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4246,17 +4246,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4324,8 +4324,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>3</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4334,37 +4336,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4389,33 +4393,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4432,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4505,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4535,33 +4539,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4578,12 +4582,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4619,9 +4623,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4651,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4681,33 +4685,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4724,12 +4728,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4763,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4797,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4827,7 +4831,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4836,24 +4840,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>8</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4870,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4909,7 +4913,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4943,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4982,11 +4986,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5016,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5055,7 +5059,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5089,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5128,11 +5132,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5162,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5201,11 +5205,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5235,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5274,11 +5278,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5308,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5347,11 +5351,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5381,12 +5385,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5411,7 +5415,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5424,7 +5428,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5437,7 +5441,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5454,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5493,11 +5497,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5527,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5566,11 +5570,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5600,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5641,9 +5645,9 @@
       <c r="I71" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5673,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5712,11 +5716,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5746,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5785,7 +5789,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5819,12 +5823,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5858,11 +5862,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5892,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5965,12 +5969,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5995,25 +5999,25 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6021,7 +6025,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6038,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6079,9 +6083,9 @@
       <c r="I77" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6111,12 +6115,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6141,7 +6145,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6150,24 +6154,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6184,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6217,13 +6221,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6257,12 +6261,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6290,17 +6294,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6330,12 +6334,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6360,59 +6364,55 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6437,33 +6437,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6518,10 +6518,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6530,39 +6528,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6587,33 +6583,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 43,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6630,12 +6626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6660,7 +6656,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6668,10 +6664,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6680,39 +6674,37 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6737,33 +6729,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6780,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6810,7 +6802,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6818,10 +6810,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6830,39 +6820,37 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6887,20 +6875,20 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6909,11 +6897,11 @@
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6930,12 +6918,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6960,7 +6948,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6968,51 +6956,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7037,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7080,12 +7064,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7110,7 +7094,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7118,10 +7102,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7130,39 +7112,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7187,7 +7167,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7196,24 +7176,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7230,12 +7210,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7260,7 +7240,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7268,51 +7248,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7340,17 +7316,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7380,12 +7356,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7419,7 +7395,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7453,12 +7429,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7483,33 +7459,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7526,12 +7502,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7567,9 +7543,9 @@
       <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7599,12 +7575,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7629,33 +7605,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7672,12 +7648,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7711,11 +7687,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7745,12 +7721,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7775,7 +7751,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7784,24 +7760,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7818,12 +7794,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7857,11 +7833,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7891,12 +7867,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7930,11 +7906,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7964,12 +7940,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8003,11 +7979,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8037,12 +8013,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8076,11 +8052,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8110,12 +8086,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8149,11 +8125,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8183,12 +8159,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8222,11 +8198,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8256,12 +8232,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8289,17 +8265,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8317,7 +8293,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
@@ -8329,12 +8305,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8362,17 +8338,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8402,12 +8378,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8432,7 +8408,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8441,24 +8417,24 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8475,12 +8451,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8505,33 +8481,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8548,12 +8524,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8578,7 +8554,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8586,51 +8562,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8655,33 +8627,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8698,12 +8670,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8728,7 +8700,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8736,51 +8708,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8805,33 +8773,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8848,12 +8816,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8887,7 +8855,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -8921,12 +8889,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8951,33 +8919,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8994,12 +8962,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9067,12 +9035,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9097,7 +9065,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9106,24 +9074,24 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>8</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9140,12 +9108,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9213,12 +9181,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9246,17 +9214,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H120" s="4" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9286,12 +9254,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9359,12 +9327,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9389,33 +9357,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>11</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9432,12 +9400,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9462,7 +9430,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9470,8 +9438,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9480,37 +9450,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9535,7 +9507,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9544,24 +9516,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▲ 266,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9578,12 +9550,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9608,55 +9580,59 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9690,11 +9666,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9724,78 +9700,3172 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 121,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L127" s="2" t="n">
+      <c r="L169" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 83,3%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1403,22 +1403,22 @@
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1622,9 +1622,9 @@
       <c r="I16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1760,17 +1760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1833,17 +1833,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2135,20 +2135,20 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2195,20 +2195,20 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2217,11 +2217,11 @@
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2276,10 +2276,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2288,41 +2286,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2345,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2388,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2418,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2426,8 +2422,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2436,39 +2434,41 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2491,20 +2491,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2513,11 +2513,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,14 +2534,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2575,9 +2575,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2607,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2637,33 +2637,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 53,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2719,11 +2719,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2792,24 +2792,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2865,11 +2865,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2938,11 +2938,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2972,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3011,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3078,17 +3078,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3221,33 +3221,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,14 +3264,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3303,11 +3303,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3372,20 +3372,20 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3410,14 +3410,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3449,11 +3449,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3522,24 +3522,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3668,11 +3668,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3954,17 +3954,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4067,14 +4067,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4097,33 +4097,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4213,14 +4213,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4243,33 +4243,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4286,14 +4286,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4324,10 +4324,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4336,41 +4334,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4393,33 +4389,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,14 +4432,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4466,7 +4462,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4474,8 +4470,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4484,39 +4482,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4552,20 +4552,20 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4582,14 +4582,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4623,9 +4623,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,14 +4655,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4688,17 +4688,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4728,14 +4728,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,14 +4801,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4831,33 +4831,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4947,14 +4947,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4986,24 +4986,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5132,11 +5132,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5239,14 +5239,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5272,17 +5272,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5353,9 +5353,9 @@
       <c r="I67" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,14 +5385,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5415,33 +5415,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5458,14 +5458,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5497,11 +5497,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5531,14 +5531,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5570,24 +5570,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5604,14 +5604,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5643,11 +5643,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,14 +5677,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5716,11 +5716,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,14 +5823,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5856,17 +5856,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,14 +5896,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5935,11 +5935,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,14 +5969,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5999,20 +5999,20 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6021,11 +6021,11 @@
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6042,14 +6042,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6081,11 +6081,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6115,14 +6115,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6150,20 +6150,20 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6188,14 +6188,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6221,13 +6221,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6261,14 +6261,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6300,24 +6300,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6334,14 +6334,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6364,20 +6364,20 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6386,11 +6386,11 @@
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,14 +6407,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6440,17 +6440,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6480,14 +6480,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6515,20 +6515,20 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6553,14 +6553,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6583,33 +6583,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 51,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6626,14 +6626,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6674,15 +6674,15 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6699,14 +6699,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6729,33 +6729,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6845,14 +6845,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6875,33 +6875,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,14 +6918,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6959,9 +6959,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6991,14 +6991,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7021,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,14 +7064,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7103,11 +7103,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,14 +7137,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7176,24 +7176,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,14 +7210,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7249,11 +7249,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7283,14 +7283,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7322,11 +7322,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7356,14 +7356,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7395,11 +7395,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7429,14 +7429,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7462,17 +7462,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7502,14 +7502,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7575,14 +7575,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7605,33 +7605,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7721,14 +7721,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7756,20 +7756,20 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7794,14 +7794,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7835,9 +7835,9 @@
       <c r="I101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7867,14 +7867,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7906,24 +7906,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>▼ 63,6%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7940,14 +7940,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7979,11 +7979,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8013,14 +8013,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8052,11 +8052,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8159,14 +8159,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8198,11 +8198,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8273,9 +8273,9 @@
       <c r="I107" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8305,14 +8305,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8338,17 +8338,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8378,14 +8378,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8417,11 +8417,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8451,14 +8451,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8481,33 +8481,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8524,14 +8524,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8563,11 +8563,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8597,14 +8597,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8627,7 +8627,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8636,24 +8636,24 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8670,12 +8670,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8711,9 +8711,9 @@
       <c r="I113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8743,14 +8743,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8782,11 +8782,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8816,14 +8816,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8855,11 +8855,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8889,14 +8889,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8922,17 +8922,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▼ 37,5%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8962,14 +8962,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9001,11 +9001,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9035,14 +9035,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9065,33 +9065,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9108,14 +9108,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9147,11 +9147,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9181,14 +9181,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9220,24 +9220,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9254,14 +9254,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9293,11 +9293,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9327,14 +9327,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9360,17 +9360,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="4" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9400,14 +9400,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9438,10 +9438,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9450,41 +9448,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9507,33 +9503,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9550,12 +9546,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9627,14 +9623,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9657,7 +9653,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9668,22 +9664,22 @@
       <c r="I126" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9700,12 +9696,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9777,14 +9773,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9810,17 +9806,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9850,12 +9846,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9927,14 +9923,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9957,16 +9953,16 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -9979,11 +9975,11 @@
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10000,12 +9996,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10077,14 +10073,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10107,20 +10103,20 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>▲ 404,8%</t>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J132" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10129,11 +10125,11 @@
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10150,12 +10146,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10227,14 +10223,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10257,33 +10253,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10300,12 +10296,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10377,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10407,33 +10403,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10450,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10480,7 +10476,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10488,8 +10484,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>0</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10498,39 +10496,41 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10553,33 +10553,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10596,14 +10596,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10637,9 +10637,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10669,14 +10669,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10699,33 +10699,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10742,14 +10742,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10781,11 +10781,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10815,14 +10815,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -10854,24 +10854,24 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10888,14 +10888,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10927,11 +10927,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10961,14 +10961,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11000,11 +11000,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11034,14 +11034,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11073,11 +11073,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11107,14 +11107,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11146,11 +11146,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11180,14 +11180,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11219,11 +11219,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11253,14 +11253,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11292,11 +11292,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>6</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11326,14 +11326,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11359,19 +11359,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
@@ -11399,14 +11399,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11438,11 +11438,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11472,14 +11472,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11502,12 +11502,12 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
@@ -11515,25 +11515,25 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11545,14 +11545,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11578,17 +11578,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11618,14 +11618,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11648,7 +11648,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11656,10 +11656,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11668,41 +11666,39 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11725,33 +11721,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11768,12 +11764,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11845,14 +11841,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11875,33 +11871,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11918,14 +11914,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11948,7 +11944,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -11956,8 +11952,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -11966,39 +11964,41 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12021,33 +12021,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,5%</t>
+        <v>12</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12064,14 +12064,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12105,9 +12105,9 @@
       <c r="I159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12137,14 +12137,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12176,24 +12176,24 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12210,14 +12210,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12249,11 +12249,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12283,14 +12283,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12316,17 +12316,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▼ 11,1%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12356,14 +12356,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12429,14 +12429,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12459,33 +12459,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>16</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12502,14 +12502,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
@@ -12575,14 +12575,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12614,24 +12614,24 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12648,14 +12648,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12681,17 +12681,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12721,14 +12721,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12760,11 +12760,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12794,78 +12794,224 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="n">
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L169" s="2" t="n">
+      <c r="L171" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M169" s="2" t="inlineStr">
+      <c r="M171" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>11</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1249,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1549,22 +1549,22 @@
       <c r="I15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1768,9 +1768,9 @@
       <c r="I18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1979,17 +1979,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2281,20 +2281,20 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2341,20 +2341,20 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2363,11 +2363,11 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2422,10 +2422,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2434,41 +2432,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2491,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2534,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2564,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2572,8 +2568,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2582,39 +2580,41 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2637,20 +2637,20 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2659,11 +2659,11 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2721,9 +2721,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,14 +2753,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2783,33 +2783,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2865,11 +2865,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2938,24 +2938,24 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3011,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3084,11 +3084,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3157,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3224,17 +3224,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3367,33 +3367,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3410,14 +3410,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3449,11 +3449,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3518,20 +3518,20 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3668,24 +3668,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3848,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4067,14 +4067,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4100,17 +4100,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4213,14 +4213,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4243,33 +4243,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4359,14 +4359,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4389,33 +4389,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4432,14 +4432,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4470,10 +4470,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4482,41 +4480,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4539,33 +4535,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4582,14 +4578,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4612,7 +4608,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4620,8 +4616,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4630,39 +4628,41 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4728,14 +4728,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4769,9 +4769,9 @@
       <c r="I59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,14 +4801,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4834,17 +4834,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,14 +4874,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4913,11 +4913,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,14 +4947,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4977,33 +4977,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5132,24 +5132,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5239,14 +5239,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5278,11 +5278,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5385,14 +5385,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5418,17 +5418,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5499,9 +5499,9 @@
       <c r="I69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5531,14 +5531,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5561,33 +5561,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5604,14 +5604,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5643,11 +5643,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,14 +5677,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5716,24 +5716,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,14 +5750,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5789,11 +5789,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,14 +5823,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5862,11 +5862,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,14 +5969,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6002,17 +6002,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,14 +6042,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6081,11 +6081,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6115,14 +6115,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6145,20 +6145,20 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6167,11 +6167,11 @@
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6188,14 +6188,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6227,11 +6227,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6261,14 +6261,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6296,20 +6296,20 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6334,14 +6334,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6367,13 +6367,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6407,14 +6407,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6437,7 +6437,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6446,24 +6446,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,14 +6480,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6510,20 +6510,20 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6532,11 +6532,11 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6553,14 +6553,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6586,17 +6586,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6626,14 +6626,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6661,20 +6661,20 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6699,14 +6699,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6729,33 +6729,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>▼ 51,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6772,14 +6772,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6820,15 +6820,15 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6845,14 +6845,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6875,33 +6875,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6991,14 +6991,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7021,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,14 +7064,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7105,9 +7105,9 @@
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,14 +7137,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7167,33 +7167,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,14 +7210,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7249,11 +7249,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7283,14 +7283,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7322,24 +7322,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7356,14 +7356,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7395,11 +7395,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7429,14 +7429,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7468,11 +7468,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7502,14 +7502,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7541,11 +7541,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7575,14 +7575,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7608,17 +7608,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7648,14 +7648,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7721,14 +7721,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7751,33 +7751,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7794,12 +7794,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7867,14 +7867,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7940,14 +7940,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7981,9 +7981,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8013,14 +8013,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8052,24 +8052,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8086,14 +8086,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8125,11 +8125,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8159,14 +8159,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8198,11 +8198,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8305,14 +8305,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8344,11 +8344,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8419,9 +8419,9 @@
       <c r="I109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8451,14 +8451,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8484,17 +8484,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8524,14 +8524,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8563,11 +8563,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8597,14 +8597,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8627,33 +8627,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8670,14 +8670,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8709,11 +8709,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8743,14 +8743,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8782,24 +8782,24 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8857,9 +8857,9 @@
       <c r="I115" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8889,14 +8889,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8962,14 +8962,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9001,11 +9001,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9035,14 +9035,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9068,17 +9068,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9108,14 +9108,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9147,11 +9147,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9181,14 +9181,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9211,33 +9211,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9254,14 +9254,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9293,11 +9293,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9327,14 +9327,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9366,24 +9366,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9400,14 +9400,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9439,11 +9439,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9473,14 +9473,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9506,17 +9506,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9546,14 +9546,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9584,10 +9584,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9596,41 +9594,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9653,33 +9649,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9696,12 +9692,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9773,14 +9769,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9803,7 +9799,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -9814,22 +9810,22 @@
       <c r="I128" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9846,12 +9842,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9923,14 +9919,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9956,17 +9952,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9996,12 +9992,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10073,14 +10069,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10103,16 +10099,16 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10125,11 +10121,11 @@
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10146,12 +10142,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10223,14 +10219,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10253,20 +10249,20 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10275,11 +10271,11 @@
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10296,12 +10292,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10373,14 +10369,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10403,33 +10399,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10446,12 +10442,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10523,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10553,33 +10549,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10596,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10626,7 +10622,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10634,8 +10630,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10644,39 +10642,41 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10699,33 +10699,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10742,14 +10742,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10783,9 +10783,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10815,14 +10815,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10845,33 +10845,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10888,14 +10888,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10927,11 +10927,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10961,14 +10961,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11000,24 +11000,24 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11034,14 +11034,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11073,11 +11073,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11107,14 +11107,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11146,11 +11146,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11180,14 +11180,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11219,11 +11219,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11253,14 +11253,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11292,11 +11292,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11326,14 +11326,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11365,11 +11365,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11399,14 +11399,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11438,11 +11438,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11472,14 +11472,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11505,19 +11505,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -11545,14 +11545,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11584,11 +11584,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11618,14 +11618,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11648,12 +11648,12 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
-        </is>
-      </c>
-      <c r="H153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
@@ -11661,25 +11661,25 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11691,14 +11691,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11724,17 +11724,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11764,14 +11764,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -11802,10 +11802,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11814,41 +11812,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11871,33 +11867,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11914,12 +11910,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11991,14 +11987,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12021,33 +12017,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12064,14 +12060,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12094,7 +12090,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12102,8 +12098,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>0</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12112,39 +12110,41 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12167,33 +12167,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12210,14 +12210,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12251,9 +12251,9 @@
       <c r="I161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12283,14 +12283,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12322,24 +12322,24 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>13</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12356,14 +12356,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12395,11 +12395,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12429,14 +12429,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12462,17 +12462,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>23</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12502,14 +12502,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12541,11 +12541,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12575,14 +12575,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12605,33 +12605,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12648,14 +12648,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12687,7 +12687,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12721,14 +12721,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -12760,24 +12760,24 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▲ 266,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12794,14 +12794,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12827,17 +12827,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12867,14 +12867,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12906,11 +12906,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12940,78 +12940,224 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="n">
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L171" s="2" t="n">
+      <c r="L173" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M171" s="2" t="inlineStr">
+      <c r="M173" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>11</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1176,17 +1176,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1395,17 +1395,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1695,22 +1695,22 @@
       <c r="I17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1914,9 +1914,9 @@
       <c r="I20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2427,20 +2427,20 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2487,20 +2487,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2509,11 +2509,11 @@
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2568,10 +2568,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2580,41 +2578,39 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2637,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2680,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2710,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2718,8 +2714,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2728,39 +2726,41 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2783,20 +2783,20 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2826,14 +2826,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2867,9 +2867,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,14 +2899,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -2929,33 +2929,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2972,14 +2972,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3011,11 +3011,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,14 +3045,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3084,24 +3084,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,14 +3118,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3157,11 +3157,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3230,11 +3230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3264,14 +3264,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3303,11 +3303,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,14 +3337,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3370,17 +3370,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,14 +3483,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3513,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,14 +3556,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,14 +3629,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3664,20 +3664,20 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3702,14 +3702,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3775,14 +3775,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3814,24 +3814,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3848,14 +3848,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,14 +3994,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4033,11 +4033,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,14 +4067,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4106,11 +4106,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4213,14 +4213,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4246,17 +4246,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4359,14 +4359,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4389,33 +4389,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4505,14 +4505,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4535,33 +4535,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4578,14 +4578,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4616,10 +4616,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4628,41 +4626,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4685,33 +4681,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4728,14 +4724,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4758,7 +4754,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4766,8 +4762,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4776,39 +4774,41 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4844,20 +4844,20 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,14 +4874,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4915,9 +4915,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,14 +4947,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -4980,17 +4980,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,14 +5020,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5059,11 +5059,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5123,33 +5123,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5239,14 +5239,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5278,24 +5278,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5385,14 +5385,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5424,11 +5424,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5531,14 +5531,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5564,17 +5564,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5645,9 +5645,9 @@
       <c r="I71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,14 +5677,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5707,33 +5707,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,14 +5750,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5789,11 +5789,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,14 +5823,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5862,24 +5862,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5896,14 +5896,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -5935,11 +5935,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,14 +5969,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6008,11 +6008,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6115,14 +6115,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6148,17 +6148,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6188,14 +6188,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6227,11 +6227,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6261,14 +6261,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6291,20 +6291,20 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6313,11 +6313,11 @@
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6334,14 +6334,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6373,11 +6373,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6407,14 +6407,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6442,20 +6442,20 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,14 +6480,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6513,13 +6513,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6553,14 +6553,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6592,24 +6592,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6626,14 +6626,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6656,20 +6656,20 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6678,11 +6678,11 @@
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6699,14 +6699,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6732,17 +6732,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6772,14 +6772,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6807,20 +6807,20 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -6845,14 +6845,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6875,33 +6875,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>▼ 51,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,14 +6918,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -6966,15 +6966,15 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6991,14 +6991,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7021,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,12 +7064,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7137,14 +7137,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7167,33 +7167,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,14 +7210,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7251,9 +7251,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7283,14 +7283,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7313,33 +7313,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7356,14 +7356,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7395,11 +7395,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7429,14 +7429,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7468,24 +7468,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7502,14 +7502,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7541,11 +7541,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7575,14 +7575,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7614,11 +7614,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7648,14 +7648,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7687,11 +7687,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7721,14 +7721,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7754,17 +7754,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7794,14 +7794,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7867,14 +7867,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -7897,33 +7897,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8013,14 +8013,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8048,20 +8048,20 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8086,14 +8086,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8127,9 +8127,9 @@
       <c r="I105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8159,14 +8159,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8198,24 +8198,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>6</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8232,14 +8232,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8271,11 +8271,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8305,14 +8305,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8344,11 +8344,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8451,14 +8451,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8490,11 +8490,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8565,9 +8565,9 @@
       <c r="I111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8597,14 +8597,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8630,17 +8630,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8670,14 +8670,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8709,11 +8709,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8743,14 +8743,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8773,33 +8773,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8816,14 +8816,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8855,11 +8855,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8889,14 +8889,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8928,24 +8928,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9003,9 +9003,9 @@
       <c r="I117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9035,14 +9035,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9074,11 +9074,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9108,14 +9108,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9147,11 +9147,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9181,14 +9181,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9214,17 +9214,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9254,14 +9254,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9293,11 +9293,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9327,14 +9327,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9357,33 +9357,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9400,14 +9400,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9439,11 +9439,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9473,14 +9473,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9512,24 +9512,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9546,14 +9546,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9619,14 +9619,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9652,17 +9652,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9692,14 +9692,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9730,10 +9730,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9742,41 +9740,39 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9799,33 +9795,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>11</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9842,12 +9838,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9919,14 +9915,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -9949,7 +9945,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -9960,22 +9956,22 @@
       <c r="I130" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -9992,12 +9988,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10069,14 +10065,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10102,17 +10098,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10142,12 +10138,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10219,14 +10215,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10249,16 +10245,16 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10271,11 +10267,11 @@
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10292,12 +10288,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10369,14 +10365,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10399,20 +10395,20 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10421,11 +10417,11 @@
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10442,12 +10438,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10519,14 +10515,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10549,33 +10545,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10592,12 +10588,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10669,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10699,33 +10695,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10742,14 +10738,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10772,7 +10768,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10780,8 +10776,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -10790,39 +10788,41 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10845,33 +10845,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 87,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10888,14 +10888,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10929,9 +10929,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10961,14 +10961,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -10991,33 +10991,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>▼ 27,3%</t>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11034,14 +11034,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11073,11 +11073,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11107,14 +11107,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11146,24 +11146,24 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11180,14 +11180,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11219,11 +11219,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11253,14 +11253,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11292,11 +11292,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11326,14 +11326,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11365,11 +11365,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11399,14 +11399,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11438,11 +11438,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11472,14 +11472,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11511,11 +11511,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11545,14 +11545,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11584,11 +11584,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11618,14 +11618,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11651,19 +11651,19 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
@@ -11691,14 +11691,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11730,11 +11730,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11764,14 +11764,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11794,12 +11794,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
@@ -11807,25 +11807,25 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11837,14 +11837,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11870,17 +11870,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11910,14 +11910,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -11948,10 +11948,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -11960,41 +11958,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>500,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12017,33 +12013,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12060,12 +12056,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12137,14 +12133,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12167,33 +12163,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12210,14 +12206,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12240,7 +12236,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12248,8 +12244,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="n">
-        <v>0</v>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12258,39 +12256,41 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12313,33 +12313,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12356,14 +12356,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12397,9 +12397,9 @@
       <c r="I163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12429,14 +12429,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12468,24 +12468,24 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>13</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12502,14 +12502,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12541,11 +12541,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12575,14 +12575,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12608,17 +12608,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>23</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12648,14 +12648,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12687,11 +12687,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12721,14 +12721,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12751,33 +12751,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 11,1%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12794,14 +12794,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -12867,14 +12867,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -12906,24 +12906,24 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 266,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12940,14 +12940,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -12973,17 +12973,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13013,14 +13013,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-098-BR</t>
@@ -13052,11 +13052,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>22</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13086,78 +13086,224 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L173" s="2" t="n">
+      <c r="L175" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M173" s="2" t="inlineStr">
+      <c r="M175" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
+++ b/saida_skus/SKU_UTD-098-BR-PORTA-ROLO-BRANCO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +963,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 83,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,16 +1474,16 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 83,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,24 +1693,24 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,16 +2350,16 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2425,22 +2425,22 @@
       <c r="I27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2655,11 +2655,11 @@
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2714,51 +2714,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2786,17 +2782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2859,17 +2855,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2929,29 +2925,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2972,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3002,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3011,24 +3007,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3045,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3075,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 53,8%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3118,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3157,7 +3153,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3191,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3221,7 +3217,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3230,11 +3226,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3243,11 +3239,11 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3264,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3294,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3302,47 +3298,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3370,17 +3370,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3449,11 +3449,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3513,33 +3513,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3595,11 +3595,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3659,25 +3659,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▲ 53,8%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3814,24 +3814,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3887,11 +3887,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3960,11 +3960,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4033,11 +4033,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4100,17 +4100,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4243,33 +4243,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4325,11 +4325,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4359,12 +4359,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4389,33 +4389,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4544,24 +4544,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4617,11 +4617,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4684,17 +4684,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4762,51 +4762,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4831,7 +4827,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4840,24 +4836,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,12 +4870,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4913,11 +4909,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,12 +4943,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4980,17 +4976,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,12 +5016,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5059,11 +5055,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5093,12 +5089,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5123,33 +5119,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 45,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,12 +5162,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5205,11 +5201,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5239,12 +5235,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5269,33 +5265,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 20,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,12 +5308,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5342,7 +5338,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5350,47 +5346,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>2</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5424,24 +5424,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5497,11 +5497,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5570,11 +5570,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5643,11 +5643,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5710,17 +5710,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5791,9 +5791,9 @@
       <c r="I73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5864,9 +5864,9 @@
       <c r="I74" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5935,11 +5935,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6008,11 +6008,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6115,12 +6115,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6154,11 +6154,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6227,11 +6227,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6373,11 +6373,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6437,25 +6437,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 20,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6553,12 +6553,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6596,20 +6596,20 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6738,11 +6738,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6802,20 +6802,20 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6824,11 +6824,11 @@
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6878,17 +6878,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6957,24 +6957,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6991,12 +6991,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7024,22 +7024,22 @@
           <t>R$ 22,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 51,1%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,12 +7064,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7137,12 +7137,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 45,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7176,24 +7176,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7243,9 +7243,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
@@ -7283,12 +7283,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7316,17 +7316,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7356,12 +7356,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7386,18 +7386,18 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -7408,11 +7408,11 @@
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7459,33 +7459,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7550,15 +7550,15 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7605,33 +7605,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>▼ 51,1%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7689,9 +7689,9 @@
       <c r="I99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 45,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7760,24 +7760,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7794,12 +7794,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7867,12 +7867,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7981,9 +7981,9 @@
       <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8048,20 +8048,20 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8159,12 +8159,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 22,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8198,24 +8198,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8232,12 +8232,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="3" t="inlineStr">
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -8305,12 +8305,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8344,11 +8344,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 63,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8417,11 +8417,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8484,17 +8484,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8563,11 +8563,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8627,33 +8627,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8670,12 +8670,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8709,11 +8709,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 22,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
@@ -8786,20 +8786,20 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8855,11 +8855,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8928,24 +8928,24 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 63,6%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9074,11 +9074,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9149,9 +9149,9 @@
       <c r="I119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9220,11 +9220,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9293,11 +9293,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9360,17 +9360,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H122" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 37,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9400,12 +9400,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9439,11 +9439,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9514,9 +9514,9 @@
       <c r="I124" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9733,9 +9733,9 @@
       <c r="I127" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9798,17 +9798,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 22,2%</t>
+        <v>6</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9838,12 +9838,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9876,10 +9876,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -9888,39 +9886,37 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9945,33 +9941,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▼ 37,5%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -9988,12 +9984,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10018,7 +10014,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10026,51 +10022,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10095,7 +10087,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10104,24 +10096,24 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,8%</t>
+        <v>8</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10138,12 +10130,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10168,7 +10160,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10176,51 +10168,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10248,17 +10236,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10288,12 +10276,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10318,7 +10306,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10326,10 +10314,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10338,39 +10324,37 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10395,20 +10379,20 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▲ 22,2%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10417,11 +10401,11 @@
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10438,12 +10422,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10515,12 +10499,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10545,33 +10529,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 404,8%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10588,12 +10572,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10665,12 +10649,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10695,7 +10679,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10704,24 +10688,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,8%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10738,12 +10722,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10815,12 +10799,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10848,17 +10832,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10888,12 +10872,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10918,7 +10902,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -10926,8 +10910,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -10936,37 +10922,39 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -10994,22 +10982,22 @@
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,2%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 87,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
@@ -11017,7 +11005,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11034,12 +11022,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11064,7 +11052,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11072,47 +11060,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11137,33 +11129,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▲ 404,8%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 27,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11180,12 +11172,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11210,7 +11202,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11218,47 +11210,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11283,7 +11279,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11292,24 +11288,24 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11326,12 +11322,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11356,7 +11352,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11364,47 +11360,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11432,17 +11432,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11545,12 +11545,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11575,33 +11575,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 87,5%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11618,12 +11618,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11659,7 +11659,7 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="3" t="inlineStr">
+      <c r="J153" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -11691,12 +11691,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 42,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11730,24 +11730,24 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 27,3%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11764,12 +11764,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11797,17 +11797,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -11837,12 +11837,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11876,11 +11876,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11910,12 +11910,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 121,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -11949,24 +11949,24 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>500,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -11983,12 +11983,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12016,17 +12016,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12056,12 +12056,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12094,10 +12094,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12106,39 +12104,37 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12163,33 +12159,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12206,12 +12202,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12236,7 +12232,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12244,51 +12240,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12313,33 +12305,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 42,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12356,12 +12348,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12389,17 +12381,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12417,7 +12409,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12429,12 +12421,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12459,7 +12451,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 21,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12468,24 +12460,24 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 43,5%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12502,12 +12494,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12532,7 +12524,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 121,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12541,24 +12533,24 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>500,0%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12575,12 +12567,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12608,17 +12600,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12648,12 +12640,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12678,7 +12670,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -12686,47 +12678,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12751,33 +12747,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 21,00</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,1%</t>
+        <v>5</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12794,12 +12790,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12824,7 +12820,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -12832,8 +12828,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="n">
-        <v>1</v>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -12842,37 +12840,39 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12900,22 +12900,22 @@
           <t>R$ 42,00</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H170" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12940,12 +12940,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21,00</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13052,24 +13052,24 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>▲ 266,7%</t>
+          <t>▼ 43,5%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13086,12 +13086,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13119,15 +13119,15 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J173" s="3" t="inlineStr">
+      <c r="J173" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -13159,12 +13159,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13198,11 +13198,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>23</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13232,78 +13232,662 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,1%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 42,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▲ 266,7%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>3861328460</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-098-BR</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Porta rolo branco</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3404789657</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-098-BR</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Porta rolo branco</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>3861328460</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 22,48</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 22,48</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 21,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="L175" s="2" t="n">
+      <c r="L183" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>